--- a/SqlServerToOracleMigrator/TableMapping.xlsx
+++ b/SqlServerToOracleMigrator/TableMapping.xlsx
@@ -46,6 +46,12 @@
     <x:t>EmptyReplacement (예: - or 'N/A')</x:t>
   </x:si>
   <x:si>
+    <x:t>AdditionalColumns (Oracle 전용 컬럼명, 쉼표 구분)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdditionalColumnsValues (값 또는 함수, 쉼표 구분)</x:t>
+  </x:si>
+  <x:si>
     <x:t>dbo.Employees</x:t>
   </x:si>
   <x:si>
@@ -55,16 +61,16 @@
     <x:t>TRUE</x:t>
   </x:si>
   <x:si>
-    <x:t>직원 정보 테이블</x:t>
+    <x:t>직원 정보 테이블 (TO_CHAR 함수 예제)</x:t>
   </x:si>
   <x:si>
     <x:t>IsActive = 1</x:t>
   </x:si>
   <x:si>
-    <x:t>EmployeeID,EmployeeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMP_ID,EMP_NAME</x:t>
+    <x:t>EmployeeID,EmployeeName,INSDTTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMP_ID,EMP_NAME,INS_DT</x:t>
   </x:si>
   <x:si>
     <x:t>EmployeeName</x:t>
@@ -73,6 +79,12 @@
     <x:t>-</x:t>
   </x:si>
   <x:si>
+    <x:t>FormattedInsDate,CreatedDate,IsDeleted,Department</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TO_CHAR({INSDTTM}, 'YYYYMMDDHHMMSSFF9'),SYSDATE,'N','HR'</x:t>
+  </x:si>
+  <x:si>
     <x:t>dbo.Departments</x:t>
   </x:si>
   <x:si>
@@ -85,6 +97,12 @@
     <x:t>FALSE</x:t>
   </x:si>
   <x:si>
+    <x:t>UpdatedDate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYSTIMESTAMP</x:t>
+  </x:si>
+  <x:si>
     <x:t>dbo.Projects</x:t>
   </x:si>
   <x:si>
@@ -95,6 +113,12 @@
   </x:si>
   <x:si>
     <x:t>Status = 'Completed'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MigrationDate,MigratedFrom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CURRENT_DATE,'SQL_Server'</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -465,7 +489,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J4"/>
+  <x:dimension ref="A1:L4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="2" width="25.710625" style="0" customWidth="1"/>
@@ -475,9 +499,10 @@
     <x:col min="6" max="6" width="16.710625" style="0" customWidth="1"/>
     <x:col min="7" max="9" width="35.710625" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="20.710625" style="0" customWidth="1"/>
+    <x:col min="11" max="12" width="40.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:10" s="1" customFormat="1">
+    <x:row r="1" spans="1:12" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -508,74 +533,98 @@
       <x:c r="J1" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:10">
+    <x:row r="2" spans="1:12">
       <x:c r="A2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:10">
+    <x:row r="3" spans="1:12">
       <x:c r="A3" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:10">
+    <x:row r="4" spans="1:12">
       <x:c r="A4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="K4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
